--- a/academias/Administración de Recursos Humanos - Estadisticos 20241.xlsx
+++ b/academias/Administración de Recursos Humanos - Estadisticos 20241.xlsx
@@ -966,25 +966,25 @@
         <v>35</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F2">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="H2" s="1">
-        <v>100</v>
+        <v>2.9</v>
       </c>
       <c r="I2" s="2">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J2">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1001,25 +1001,25 @@
         <v>21</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F3">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H3" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I3" s="2">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="J3">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1036,25 +1036,25 @@
         <v>23</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F4">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>95.7</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>4.3</v>
       </c>
       <c r="I4" s="2">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J4">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1068,25 +1068,25 @@
         <v>79</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="F5">
-        <v>79</v>
+        <v>2</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="H5" s="1">
-        <v>100</v>
+        <v>2.5</v>
       </c>
       <c r="I5" s="2">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="J5">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1103,25 +1103,25 @@
         <v>23</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F6">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H6" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I6" s="2">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J6">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1135,25 +1135,25 @@
         <v>23</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F7">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H7" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I7" s="2">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J7">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1170,25 +1170,25 @@
         <v>35</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F8">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H8" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I8" s="2">
-        <v>0</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J8">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1205,25 +1205,25 @@
         <v>21</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F9">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>95.2</v>
       </c>
       <c r="H9" s="1">
-        <v>100</v>
+        <v>4.8</v>
       </c>
       <c r="I9" s="2">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="J9">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1240,25 +1240,25 @@
         <v>40</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F10">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H10" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I10" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J10">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1275,25 +1275,25 @@
         <v>40</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F11">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H11" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I11" s="2">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="J11">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1307,25 +1307,25 @@
         <v>136</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>135</v>
       </c>
       <c r="F12">
-        <v>136</v>
+        <v>1</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>99.3</v>
       </c>
       <c r="H12" s="1">
-        <v>100</v>
+        <v>0.7</v>
       </c>
       <c r="I12" s="2">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J12">
-        <v>136</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -1336,25 +1336,25 @@
         <v>238</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>235</v>
       </c>
       <c r="F13">
-        <v>238</v>
+        <v>3</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>98.7</v>
       </c>
       <c r="H13" s="1">
-        <v>100</v>
+        <v>1.3</v>
       </c>
       <c r="I13" s="2">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="J13">
-        <v>238</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1422,19 +1422,19 @@
         <v>35</v>
       </c>
       <c r="E2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G2" s="1">
-        <v>94.3</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="H2" s="1">
-        <v>5.7</v>
+        <v>2.9</v>
       </c>
       <c r="I2" s="2">
-        <v>8.800000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -1457,19 +1457,19 @@
         <v>21</v>
       </c>
       <c r="E3">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" s="1">
-        <v>95.2</v>
+        <v>100</v>
       </c>
       <c r="H3" s="1">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="I3" s="2">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -1504,7 +1504,7 @@
         <v>4.3</v>
       </c>
       <c r="I4" s="2">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -1524,19 +1524,19 @@
         <v>79</v>
       </c>
       <c r="E5">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G5" s="1">
-        <v>94.90000000000001</v>
+        <v>97.5</v>
       </c>
       <c r="H5" s="1">
-        <v>5.1</v>
+        <v>2.5</v>
       </c>
       <c r="I5" s="2">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1559,19 +1559,19 @@
         <v>23</v>
       </c>
       <c r="E6">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" s="1">
-        <v>95.7</v>
+        <v>100</v>
       </c>
       <c r="H6" s="1">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="I6" s="2">
-        <v>8.5</v>
+        <v>8.9</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -1591,19 +1591,19 @@
         <v>23</v>
       </c>
       <c r="E7">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" s="1">
-        <v>95.7</v>
+        <v>100</v>
       </c>
       <c r="H7" s="1">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="I7" s="2">
-        <v>8.5</v>
+        <v>8.9</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -1626,19 +1626,19 @@
         <v>35</v>
       </c>
       <c r="E8">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" s="1">
-        <v>97.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="H8" s="1">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="I8" s="2">
-        <v>8.5</v>
+        <v>9.4</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -1673,7 +1673,7 @@
         <v>4.8</v>
       </c>
       <c r="I9" s="2">
-        <v>6.3</v>
+        <v>7.1</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -1708,7 +1708,7 @@
         <v>0</v>
       </c>
       <c r="I10" s="2">
-        <v>7.3</v>
+        <v>7.8</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -1743,7 +1743,7 @@
         <v>0</v>
       </c>
       <c r="I11" s="2">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -1763,19 +1763,19 @@
         <v>136</v>
       </c>
       <c r="E12">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G12" s="1">
-        <v>98.5</v>
+        <v>99.3</v>
       </c>
       <c r="H12" s="1">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="I12" s="2">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -1792,19 +1792,19 @@
         <v>238</v>
       </c>
       <c r="E13">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="F13">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G13" s="1">
-        <v>97.09999999999999</v>
+        <v>98.7</v>
       </c>
       <c r="H13" s="1">
-        <v>2.9</v>
+        <v>1.3</v>
       </c>
       <c r="I13" s="2">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="J13">
         <v>0</v>

--- a/academias/Administración de Recursos Humanos - Estadisticos 20241.xlsx
+++ b/academias/Administración de Recursos Humanos - Estadisticos 20241.xlsx
@@ -577,28 +577,28 @@
         <v>22</v>
       </c>
       <c r="D4">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E4">
         <v>22</v>
       </c>
       <c r="F4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G4" s="1">
-        <v>95.7</v>
+        <v>91.7</v>
       </c>
       <c r="H4" s="1">
-        <v>4.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I4" s="2">
         <v>9</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" s="1">
-        <v>0</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -609,28 +609,28 @@
         <v>16</v>
       </c>
       <c r="D5">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E5">
         <v>75</v>
       </c>
       <c r="F5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G5" s="1">
-        <v>94.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="H5" s="1">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="I5" s="2">
         <v>8.6</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" s="1">
-        <v>0</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -644,28 +644,28 @@
         <v>22</v>
       </c>
       <c r="D6">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E6">
         <v>22</v>
       </c>
       <c r="F6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G6" s="1">
-        <v>95.7</v>
+        <v>91.7</v>
       </c>
       <c r="H6" s="1">
-        <v>4.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I6" s="2">
         <v>8.5</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" s="1">
-        <v>0</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -676,28 +676,28 @@
         <v>16</v>
       </c>
       <c r="D7">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E7">
         <v>22</v>
       </c>
       <c r="F7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G7" s="1">
-        <v>95.7</v>
+        <v>91.7</v>
       </c>
       <c r="H7" s="1">
-        <v>4.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I7" s="2">
         <v>8.5</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" s="1">
-        <v>0</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -781,10 +781,10 @@
         <v>23</v>
       </c>
       <c r="D10">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E10">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -796,7 +796,7 @@
         <v>0</v>
       </c>
       <c r="I10" s="2">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -816,10 +816,10 @@
         <v>23</v>
       </c>
       <c r="D11">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E11">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -831,7 +831,7 @@
         <v>0</v>
       </c>
       <c r="I11" s="2">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -848,19 +848,19 @@
         <v>16</v>
       </c>
       <c r="D12">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="E12">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="F12">
         <v>2</v>
       </c>
       <c r="G12" s="1">
-        <v>98.5</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="H12" s="1">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="I12" s="2">
         <v>7.4</v>
@@ -877,28 +877,28 @@
         <v>19</v>
       </c>
       <c r="D13">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="E13">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="F13">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G13" s="1">
-        <v>97.09999999999999</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="H13" s="1">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="I13" s="2">
         <v>8</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K13" s="1">
-        <v>0</v>
+        <v>0.8</v>
       </c>
     </row>
   </sheetData>
@@ -1033,28 +1033,28 @@
         <v>22</v>
       </c>
       <c r="D4">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E4">
         <v>22</v>
       </c>
       <c r="F4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G4" s="1">
-        <v>95.7</v>
+        <v>91.7</v>
       </c>
       <c r="H4" s="1">
-        <v>4.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I4" s="2">
         <v>8.699999999999999</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" s="1">
-        <v>0</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1065,28 +1065,28 @@
         <v>16</v>
       </c>
       <c r="D5">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E5">
         <v>77</v>
       </c>
       <c r="F5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G5" s="1">
-        <v>97.5</v>
+        <v>96.2</v>
       </c>
       <c r="H5" s="1">
-        <v>2.5</v>
+        <v>3.8</v>
       </c>
       <c r="I5" s="2">
         <v>8.4</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" s="1">
-        <v>0</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1100,28 +1100,28 @@
         <v>22</v>
       </c>
       <c r="D6">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E6">
         <v>23</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" s="1">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="H6" s="1">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="I6" s="2">
         <v>8.699999999999999</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" s="1">
-        <v>0</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1132,28 +1132,28 @@
         <v>16</v>
       </c>
       <c r="D7">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E7">
         <v>23</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" s="1">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="H7" s="1">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="I7" s="2">
         <v>8.699999999999999</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" s="1">
-        <v>0</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1237,10 +1237,10 @@
         <v>23</v>
       </c>
       <c r="D10">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E10">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -1252,7 +1252,7 @@
         <v>0</v>
       </c>
       <c r="I10" s="2">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -1272,10 +1272,10 @@
         <v>23</v>
       </c>
       <c r="D11">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E11">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -1287,7 +1287,7 @@
         <v>0</v>
       </c>
       <c r="I11" s="2">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -1304,10 +1304,10 @@
         <v>16</v>
       </c>
       <c r="D12">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="E12">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="F12">
         <v>1</v>
@@ -1319,7 +1319,7 @@
         <v>0.7</v>
       </c>
       <c r="I12" s="2">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -1333,28 +1333,28 @@
         <v>19</v>
       </c>
       <c r="D13">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="E13">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="F13">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G13" s="1">
-        <v>98.7</v>
+        <v>98</v>
       </c>
       <c r="H13" s="1">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="I13" s="2">
         <v>8.4</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K13" s="1">
-        <v>0</v>
+        <v>0.8</v>
       </c>
     </row>
   </sheetData>
@@ -1422,19 +1422,19 @@
         <v>35</v>
       </c>
       <c r="E2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2" s="1">
-        <v>97.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="H2" s="1">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="I2" s="2">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -1469,7 +1469,7 @@
         <v>0</v>
       </c>
       <c r="I3" s="2">
-        <v>8.1</v>
+        <v>7.8</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -1489,28 +1489,28 @@
         <v>22</v>
       </c>
       <c r="D4">
+        <v>24</v>
+      </c>
+      <c r="E4">
         <v>23</v>
       </c>
-      <c r="E4">
-        <v>22</v>
-      </c>
       <c r="F4">
         <v>1</v>
       </c>
       <c r="G4" s="1">
-        <v>95.7</v>
+        <v>95.8</v>
       </c>
       <c r="H4" s="1">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I4" s="2">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" s="1">
-        <v>0</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1521,28 +1521,28 @@
         <v>16</v>
       </c>
       <c r="D5">
+        <v>80</v>
+      </c>
+      <c r="E5">
         <v>79</v>
       </c>
-      <c r="E5">
-        <v>77</v>
-      </c>
       <c r="F5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G5" s="1">
-        <v>97.5</v>
+        <v>98.8</v>
       </c>
       <c r="H5" s="1">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
       <c r="I5" s="2">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" s="1">
-        <v>0</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1556,28 +1556,28 @@
         <v>22</v>
       </c>
       <c r="D6">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E6">
         <v>23</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" s="1">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="H6" s="1">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="I6" s="2">
         <v>8.9</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" s="1">
-        <v>0</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1588,28 +1588,28 @@
         <v>16</v>
       </c>
       <c r="D7">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E7">
         <v>23</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" s="1">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="H7" s="1">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="I7" s="2">
         <v>8.9</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" s="1">
-        <v>0</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1638,7 +1638,7 @@
         <v>0</v>
       </c>
       <c r="I8" s="2">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -1673,7 +1673,7 @@
         <v>4.8</v>
       </c>
       <c r="I9" s="2">
-        <v>7.1</v>
+        <v>6.8</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -1693,10 +1693,10 @@
         <v>23</v>
       </c>
       <c r="D10">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E10">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -1708,7 +1708,7 @@
         <v>0</v>
       </c>
       <c r="I10" s="2">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -1728,10 +1728,10 @@
         <v>23</v>
       </c>
       <c r="D11">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E11">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -1743,7 +1743,7 @@
         <v>0</v>
       </c>
       <c r="I11" s="2">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -1760,10 +1760,10 @@
         <v>16</v>
       </c>
       <c r="D12">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="E12">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="F12">
         <v>1</v>
@@ -1789,28 +1789,28 @@
         <v>19</v>
       </c>
       <c r="D13">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="E13">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="F13">
         <v>3</v>
       </c>
       <c r="G13" s="1">
-        <v>98.7</v>
+        <v>98.8</v>
       </c>
       <c r="H13" s="1">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="I13" s="2">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K13" s="1">
-        <v>0</v>
+        <v>0.8</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Administración de Recursos Humanos - Estadisticos 20241.xlsx
+++ b/academias/Administración de Recursos Humanos - Estadisticos 20241.xlsx
@@ -647,25 +647,25 @@
         <v>24</v>
       </c>
       <c r="E6">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G6" s="1">
-        <v>91.7</v>
+        <v>95.8</v>
       </c>
       <c r="H6" s="1">
-        <v>8.300000000000001</v>
+        <v>4.2</v>
       </c>
       <c r="I6" s="2">
         <v>8.5</v>
       </c>
       <c r="J6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>4.17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -679,25 +679,25 @@
         <v>24</v>
       </c>
       <c r="E7">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G7" s="1">
-        <v>91.7</v>
+        <v>95.8</v>
       </c>
       <c r="H7" s="1">
-        <v>8.300000000000001</v>
+        <v>4.2</v>
       </c>
       <c r="I7" s="2">
         <v>8.5</v>
       </c>
       <c r="J7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>4.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -880,25 +880,25 @@
         <v>248</v>
       </c>
       <c r="E13">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G13" s="1">
-        <v>96.40000000000001</v>
+        <v>96.8</v>
       </c>
       <c r="H13" s="1">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="I13" s="2">
         <v>8</v>
       </c>
       <c r="J13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K13" s="1">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
     </row>
   </sheetData>
@@ -1103,25 +1103,25 @@
         <v>24</v>
       </c>
       <c r="E6">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" s="1">
-        <v>95.8</v>
+        <v>100</v>
       </c>
       <c r="H6" s="1">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="I6" s="2">
         <v>8.699999999999999</v>
       </c>
       <c r="J6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>4.17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1135,25 +1135,25 @@
         <v>24</v>
       </c>
       <c r="E7">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" s="1">
-        <v>95.8</v>
+        <v>100</v>
       </c>
       <c r="H7" s="1">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="I7" s="2">
         <v>8.699999999999999</v>
       </c>
       <c r="J7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>4.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1336,25 +1336,25 @@
         <v>248</v>
       </c>
       <c r="E13">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F13">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G13" s="1">
-        <v>98</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="H13" s="1">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="I13" s="2">
         <v>8.4</v>
       </c>
       <c r="J13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K13" s="1">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
     </row>
   </sheetData>
@@ -1559,25 +1559,25 @@
         <v>24</v>
       </c>
       <c r="E6">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" s="1">
-        <v>95.8</v>
+        <v>100</v>
       </c>
       <c r="H6" s="1">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="I6" s="2">
-        <v>8.9</v>
+        <v>8.6</v>
       </c>
       <c r="J6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>4.17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1591,25 +1591,25 @@
         <v>24</v>
       </c>
       <c r="E7">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" s="1">
-        <v>95.8</v>
+        <v>100</v>
       </c>
       <c r="H7" s="1">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="I7" s="2">
-        <v>8.9</v>
+        <v>8.6</v>
       </c>
       <c r="J7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>4.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1792,25 +1792,25 @@
         <v>248</v>
       </c>
       <c r="E13">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G13" s="1">
-        <v>98.8</v>
+        <v>99.2</v>
       </c>
       <c r="H13" s="1">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="I13" s="2">
         <v>8.300000000000001</v>
       </c>
       <c r="J13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K13" s="1">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Administración de Recursos Humanos - Estadisticos 20241.xlsx
+++ b/academias/Administración de Recursos Humanos - Estadisticos 20241.xlsx
@@ -580,25 +580,25 @@
         <v>24</v>
       </c>
       <c r="E4">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G4" s="1">
-        <v>91.7</v>
+        <v>95.8</v>
       </c>
       <c r="H4" s="1">
-        <v>8.300000000000001</v>
+        <v>4.2</v>
       </c>
       <c r="I4" s="2">
         <v>9</v>
       </c>
       <c r="J4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>4.17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -612,25 +612,25 @@
         <v>80</v>
       </c>
       <c r="E5">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F5">
+        <v>4</v>
+      </c>
+      <c r="G5" s="1">
+        <v>95</v>
+      </c>
+      <c r="H5" s="1">
         <v>5</v>
-      </c>
-      <c r="G5" s="1">
-        <v>93.8</v>
-      </c>
-      <c r="H5" s="1">
-        <v>6.2</v>
       </c>
       <c r="I5" s="2">
         <v>8.6</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>1.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -880,25 +880,25 @@
         <v>248</v>
       </c>
       <c r="E13">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G13" s="1">
-        <v>96.8</v>
+        <v>97.2</v>
       </c>
       <c r="H13" s="1">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="I13" s="2">
         <v>8</v>
       </c>
       <c r="J13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>0.4</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1036,25 +1036,25 @@
         <v>24</v>
       </c>
       <c r="E4">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G4" s="1">
-        <v>91.7</v>
+        <v>95.8</v>
       </c>
       <c r="H4" s="1">
-        <v>8.300000000000001</v>
+        <v>4.2</v>
       </c>
       <c r="I4" s="2">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>4.17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1068,25 +1068,25 @@
         <v>80</v>
       </c>
       <c r="E5">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G5" s="1">
-        <v>96.2</v>
+        <v>97.5</v>
       </c>
       <c r="H5" s="1">
-        <v>3.8</v>
+        <v>2.5</v>
       </c>
       <c r="I5" s="2">
         <v>8.4</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>1.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1336,25 +1336,25 @@
         <v>248</v>
       </c>
       <c r="E13">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G13" s="1">
-        <v>98.40000000000001</v>
+        <v>98.8</v>
       </c>
       <c r="H13" s="1">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="I13" s="2">
         <v>8.4</v>
       </c>
       <c r="J13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>0.4</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1492,25 +1492,25 @@
         <v>24</v>
       </c>
       <c r="E4">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4" s="1">
-        <v>95.8</v>
+        <v>100</v>
       </c>
       <c r="H4" s="1">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="I4" s="2">
         <v>9</v>
       </c>
       <c r="J4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>4.17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1524,25 +1524,25 @@
         <v>80</v>
       </c>
       <c r="E5">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" s="1">
-        <v>98.8</v>
+        <v>100</v>
       </c>
       <c r="H5" s="1">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="I5" s="2">
         <v>8.6</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>1.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1792,25 +1792,25 @@
         <v>248</v>
       </c>
       <c r="E13">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G13" s="1">
-        <v>99.2</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="H13" s="1">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="I13" s="2">
         <v>8.300000000000001</v>
       </c>
       <c r="J13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>0.4</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
